--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>85.85981531331507</v>
+        <v>13.9522199884137</v>
       </c>
       <c r="D2" t="n">
-        <v>86.17236741738263</v>
+        <v>14.00300970532468</v>
       </c>
       <c r="E2" t="n">
-        <v>11.29883203011911</v>
+        <v>1.836060204894356</v>
       </c>
       <c r="F2" t="n">
-        <v>11.42830188128803</v>
+        <v>1.857099055709305</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>76.20879076470422</v>
+        <v>12.38392849926444</v>
       </c>
       <c r="D3" t="n">
-        <v>76.47751301194209</v>
+        <v>12.42759586444059</v>
       </c>
       <c r="E3" t="n">
-        <v>11.29883203011911</v>
+        <v>1.836060204894356</v>
       </c>
       <c r="F3" t="n">
-        <v>11.42830188128803</v>
+        <v>1.857099055709305</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.82531203349421</v>
+        <v>9.884113205442809</v>
       </c>
       <c r="D4" t="n">
-        <v>61.07635864470112</v>
+        <v>9.924908279763933</v>
       </c>
       <c r="E4" t="n">
-        <v>11.29883203011911</v>
+        <v>1.836060204894356</v>
       </c>
       <c r="F4" t="n">
-        <v>11.42830188128803</v>
+        <v>1.857099055709305</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>70.01155905468693</v>
+        <v>11.37687834638663</v>
       </c>
       <c r="D5" t="n">
-        <v>70.2156456489564</v>
+        <v>11.41004241795541</v>
       </c>
       <c r="E5" t="n">
-        <v>11.29883203011911</v>
+        <v>1.836060204894356</v>
       </c>
       <c r="F5" t="n">
-        <v>11.42830188128803</v>
+        <v>1.857099055709305</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>67.68254626976307</v>
+        <v>10.9984137688365</v>
       </c>
       <c r="D6" t="n">
-        <v>67.85090226965613</v>
+        <v>11.02577161881912</v>
       </c>
       <c r="E6" t="n">
-        <v>11.29883203011911</v>
+        <v>1.836060204894356</v>
       </c>
       <c r="F6" t="n">
-        <v>11.42830188128803</v>
+        <v>1.857099055709305</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>80.08415513130518</v>
+        <v>13.01367520883709</v>
       </c>
       <c r="D7" t="n">
-        <v>80.16250586196843</v>
+        <v>13.02640720256987</v>
       </c>
       <c r="E7" t="n">
-        <v>11.29883203011911</v>
+        <v>1.836060204894356</v>
       </c>
       <c r="F7" t="n">
-        <v>11.42830188128803</v>
+        <v>1.857099055709305</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>65.47740487416377</v>
+        <v>10.64007829205161</v>
       </c>
       <c r="D8" t="n">
-        <v>65.38897132241193</v>
+        <v>10.62570783989194</v>
       </c>
       <c r="E8" t="n">
-        <v>11.29883203011911</v>
+        <v>1.836060204894356</v>
       </c>
       <c r="F8" t="n">
-        <v>11.42830188128803</v>
+        <v>1.857099055709305</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>86.72856304209712</v>
+        <v>14.09339149434078</v>
       </c>
       <c r="D9" t="n">
-        <v>86.70050818461708</v>
+        <v>14.08883258000028</v>
       </c>
       <c r="E9" t="n">
-        <v>11.29883203011911</v>
+        <v>1.836060204894356</v>
       </c>
       <c r="F9" t="n">
-        <v>11.42830188128803</v>
+        <v>1.857099055709305</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>66.17936218907528</v>
+        <v>10.75414635572473</v>
       </c>
       <c r="D10" t="n">
-        <v>65.91819435089639</v>
+        <v>10.71170658202066</v>
       </c>
       <c r="E10" t="n">
-        <v>11.29883203011911</v>
+        <v>1.836060204894356</v>
       </c>
       <c r="F10" t="n">
-        <v>11.42830188128803</v>
+        <v>1.857099055709305</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>52.35857785423452</v>
+        <v>8.508268901313109</v>
       </c>
       <c r="D11" t="n">
-        <v>52.05497245595184</v>
+        <v>8.458933024092174</v>
       </c>
       <c r="E11" t="n">
-        <v>11.29883203011911</v>
+        <v>1.836060204894356</v>
       </c>
       <c r="F11" t="n">
-        <v>11.42830188128803</v>
+        <v>1.857099055709305</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.08349865956975</v>
+        <v>7.326068532180084</v>
       </c>
       <c r="D12" t="n">
-        <v>44.78357585679338</v>
+        <v>7.277331076728925</v>
       </c>
       <c r="E12" t="n">
-        <v>11.29883203011911</v>
+        <v>1.836060204894356</v>
       </c>
       <c r="F12" t="n">
-        <v>11.42830188128803</v>
+        <v>1.857099055709305</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>73.77113747014485</v>
+        <v>11.98780983889854</v>
       </c>
       <c r="D13" t="n">
-        <v>73.48446027648156</v>
+        <v>11.94122479492825</v>
       </c>
       <c r="E13" t="n">
-        <v>11.29883203011911</v>
+        <v>1.836060204894356</v>
       </c>
       <c r="F13" t="n">
-        <v>11.42830188128803</v>
+        <v>1.857099055709305</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>62.81885705705963</v>
+        <v>10.20806427177219</v>
       </c>
       <c r="D14" t="n">
-        <v>62.51157889506703</v>
+        <v>10.15813157044839</v>
       </c>
       <c r="E14" t="n">
-        <v>11.29883203011911</v>
+        <v>1.836060204894356</v>
       </c>
       <c r="F14" t="n">
-        <v>11.42830188128803</v>
+        <v>1.857099055709305</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>64.6492010759</v>
+        <v>10.50549517483375</v>
       </c>
       <c r="D15" t="n">
-        <v>64.36885977653144</v>
+        <v>10.45993971368636</v>
       </c>
       <c r="E15" t="n">
-        <v>11.29883203011911</v>
+        <v>1.836060204894356</v>
       </c>
       <c r="F15" t="n">
-        <v>11.42830188128803</v>
+        <v>1.857099055709305</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
